--- a/4993_Intercuenca_Medio_Bajo_Ucayali/_raw_reportes_xlsx/IDConfig_65263_completo.xlsx
+++ b/4993_Intercuenca_Medio_Bajo_Ucayali/_raw_reportes_xlsx/IDConfig_65263_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R311e3eccd652453e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R68dd6eee7075465e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,186 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.7150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0633</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.6550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>08/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    200.0600</x:v>
+        <x:v>    200.0500</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/4993_Intercuenca_Medio_Bajo_Ucayali/_raw_reportes_xlsx/IDConfig_65263_completo.xlsx
+++ b/4993_Intercuenca_Medio_Bajo_Ucayali/_raw_reportes_xlsx/IDConfig_65263_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R68dd6eee7075465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R90ace5f882bc48c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,741 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.9950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.6150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.8050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>20/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    201.8200</x:v>
+        <x:v>    201.6600</x:v>
       </x:c>
     </x:row>
     <x:row>
